--- a/data/trans_dic/P0901-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,36</t>
+          <t>6,23; 10,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 15,5</t>
+          <t>10,44; 15,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 15,97</t>
+          <t>10,49; 15,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,41; 18,06</t>
+          <t>12,49; 17,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,2; 15,11</t>
+          <t>10,34; 15,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,98; 25,29</t>
+          <t>18,43; 25,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,41; 26,97</t>
+          <t>20,4; 27,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,1; 22,66</t>
+          <t>18,28; 22,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,17</t>
+          <t>8,98; 12,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,46; 19,59</t>
+          <t>15,5; 19,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 20,37</t>
+          <t>16,33; 20,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,11; 19,75</t>
+          <t>16,08; 19,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,1</t>
+          <t>8,06; 11,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,74; 15,01</t>
+          <t>10,62; 14,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,07</t>
+          <t>8,29; 11,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 13,11</t>
+          <t>4,35; 12,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 18,81</t>
+          <t>14,04; 18,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,99; 25,07</t>
+          <t>19,95; 25,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,31; 20,51</t>
+          <t>15,3; 20,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,21; 22,28</t>
+          <t>18,4; 22,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,37; 14,47</t>
+          <t>11,43; 14,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,86; 19,33</t>
+          <t>16,02; 19,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,43; 15,66</t>
+          <t>12,41; 15,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 16,73</t>
+          <t>9,59; 16,83</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 11,05</t>
+          <t>6,69; 11,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 12,17</t>
+          <t>7,64; 12,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,7</t>
+          <t>6,52; 10,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 18,02</t>
+          <t>12,81; 18,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,89; 20,45</t>
+          <t>14,8; 20,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,69; 21,66</t>
+          <t>15,7; 21,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,58; 21,47</t>
+          <t>15,8; 21,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,14; 19,95</t>
+          <t>7,07; 19,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 14,98</t>
+          <t>11,31; 15,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,28; 15,99</t>
+          <t>12,47; 16,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,86; 15,44</t>
+          <t>11,74; 15,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 17,64</t>
+          <t>10,23; 17,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,11</t>
+          <t>7,57; 11,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,24; 14,97</t>
+          <t>10,38; 14,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,31</t>
+          <t>8,92; 13,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 16,68</t>
+          <t>11,99; 16,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,98; 20,79</t>
+          <t>15,77; 20,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 22,96</t>
+          <t>17,97; 22,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 21,8</t>
+          <t>16,62; 21,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 23,32</t>
+          <t>17,15; 23,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,36; 15,44</t>
+          <t>12,45; 15,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,99; 18,33</t>
+          <t>15,03; 18,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 16,93</t>
+          <t>13,45; 16,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,72; 19,63</t>
+          <t>15,59; 19,44</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,07; 10,11</t>
+          <t>8,08; 10,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,01; 13,2</t>
+          <t>10,89; 13,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 11,57</t>
+          <t>9,52; 11,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,31; 14,55</t>
+          <t>9,95; 14,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,01; 17,65</t>
+          <t>15,11; 17,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,46; 22,09</t>
+          <t>19,41; 22,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,1; 20,89</t>
+          <t>18,04; 20,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 20,78</t>
+          <t>15,48; 20,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,96; 13,66</t>
+          <t>11,95; 13,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,63; 17,46</t>
+          <t>15,6; 17,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,15; 15,96</t>
+          <t>14,23; 15,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 17,3</t>
+          <t>13,91; 17,4</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43257; 71925</t>
+          <t>43248; 71649</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73421; 109073</t>
+          <t>73477; 110183</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>72000; 107797</t>
+          <t>70780; 107138</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78800; 114638</t>
+          <t>79289; 114124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>70218; 104010</t>
+          <t>71155; 105536</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>132269; 176301</t>
+          <t>128489; 174328</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>137344; 181477</t>
+          <t>137242; 183390</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>122192; 152985</t>
+          <t>123448; 155201</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>122907; 168298</t>
+          <t>124085; 167001</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>216501; 274310</t>
+          <t>217049; 273249</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>220638; 274532</t>
+          <t>220108; 277933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>211009; 258789</t>
+          <t>210660; 260361</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77619; 116422</t>
+          <t>77493; 114858</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>109305; 152842</t>
+          <t>108130; 152123</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84221; 123361</t>
+          <t>84792; 121348</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62611; 156370</t>
+          <t>51935; 154950</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>135176; 182148</t>
+          <t>135981; 183848</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>206376; 258793</t>
+          <t>205873; 262494</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>159720; 213935</t>
+          <t>159562; 213948</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>174274; 213276</t>
+          <t>176106; 216834</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>219547; 279371</t>
+          <t>220557; 282358</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>325168; 396342</t>
+          <t>328414; 399549</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>256808; 323427</t>
+          <t>256244; 324916</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>201863; 359663</t>
+          <t>206070; 361848</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44882; 74942</t>
+          <t>45379; 74914</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>56893; 92184</t>
+          <t>57915; 94288</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49744; 81306</t>
+          <t>49534; 80607</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89374; 126968</t>
+          <t>90256; 127607</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>101818; 139836</t>
+          <t>101186; 142351</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>121960; 168348</t>
+          <t>122002; 167024</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>122281; 168529</t>
+          <t>124032; 168839</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75934; 186238</t>
+          <t>66030; 185456</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154038; 204025</t>
+          <t>154112; 204754</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>188427; 245380</t>
+          <t>191419; 248391</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183257; 238524</t>
+          <t>181282; 241413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>162320; 288954</t>
+          <t>167528; 292270</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69571; 104675</t>
+          <t>71366; 105987</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97036; 141882</t>
+          <t>98334; 141370</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83366; 124763</t>
+          <t>83649; 123242</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>111823; 154296</t>
+          <t>110896; 152129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>165954; 215956</t>
+          <t>163783; 214830</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>187948; 241563</t>
+          <t>189022; 240934</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>172854; 227536</t>
+          <t>173488; 228333</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>185238; 255382</t>
+          <t>187818; 259044</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>244869; 305743</t>
+          <t>246602; 308948</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>299762; 366555</t>
+          <t>300559; 365555</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>270275; 335385</t>
+          <t>266461; 335079</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>317532; 396488</t>
+          <t>315034; 392635</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>264385; 331126</t>
+          <t>264894; 336158</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>377124; 452238</t>
+          <t>373017; 456133</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>322135; 392663</t>
+          <t>323257; 393536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>356462; 503192</t>
+          <t>344105; 500524</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>507095; 596362</t>
+          <t>510656; 594358</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>692353; 785922</t>
+          <t>690758; 793204</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>641640; 740543</t>
+          <t>639480; 736634</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>559095; 760672</t>
+          <t>566674; 762632</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>795998; 909314</t>
+          <t>795588; 900460</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1091513; 1219392</t>
+          <t>1089810; 1217156</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>981712; 1107494</t>
+          <t>987151; 1107887</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1003297; 1231605</t>
+          <t>990136; 1238738</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0901-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P0901-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,32</t>
+          <t>6,29; 10,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,44; 15,66</t>
+          <t>10,19; 15,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,88</t>
+          <t>10,54; 15,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 17,97</t>
+          <t>12,33; 17,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,34; 15,33</t>
+          <t>10,01; 15,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,43; 25,01</t>
+          <t>18,92; 25,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,4; 27,26</t>
+          <t>20,06; 26,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18,28; 22,99</t>
+          <t>18,36; 23,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,08</t>
+          <t>8,91; 12,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,5; 19,51</t>
+          <t>15,4; 19,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,33; 20,62</t>
+          <t>16,2; 20,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,08; 19,87</t>
+          <t>16,02; 19,81</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,94</t>
+          <t>8,04; 11,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,62; 14,94</t>
+          <t>10,37; 14,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,29; 11,87</t>
+          <t>8,13; 12,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,99</t>
+          <t>10,02; 14,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,04; 18,98</t>
+          <t>13,68; 18,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,95; 25,43</t>
+          <t>19,89; 25,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,3; 20,51</t>
+          <t>15,36; 20,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 22,66</t>
+          <t>18,49; 22,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 14,63</t>
+          <t>11,57; 14,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,02; 19,49</t>
+          <t>15,89; 19,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 15,73</t>
+          <t>12,42; 15,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 16,83</t>
+          <t>14,71; 17,69</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,04</t>
+          <t>6,56; 10,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 12,45</t>
+          <t>7,66; 12,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,61</t>
+          <t>6,49; 10,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,81; 18,11</t>
+          <t>12,0; 17,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,8; 20,82</t>
+          <t>15,0; 20,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,7; 21,49</t>
+          <t>15,82; 21,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 21,51</t>
+          <t>16,02; 21,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 19,87</t>
+          <t>17,6; 22,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 15,03</t>
+          <t>11,32; 14,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,47; 16,18</t>
+          <t>12,42; 16,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,63</t>
+          <t>11,69; 15,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 17,84</t>
+          <t>15,45; 18,97</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,25</t>
+          <t>7,54; 11,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 14,92</t>
+          <t>10,41; 14,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,14</t>
+          <t>9,06; 13,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,99; 16,44</t>
+          <t>11,77; 16,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 20,68</t>
+          <t>15,72; 20,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,97; 22,9</t>
+          <t>17,78; 22,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,62; 21,88</t>
+          <t>16,47; 21,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,15; 23,66</t>
+          <t>19,95; 24,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,45; 15,6</t>
+          <t>12,56; 15,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,03; 18,28</t>
+          <t>14,88; 18,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,45; 16,91</t>
+          <t>13,52; 17,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,59; 19,44</t>
+          <t>16,58; 19,57</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,08; 10,26</t>
+          <t>8,13; 10,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,31</t>
+          <t>10,88; 13,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 11,59</t>
+          <t>9,42; 11,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,95; 14,48</t>
+          <t>12,41; 14,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,11; 17,59</t>
+          <t>15,08; 17,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,41; 22,29</t>
+          <t>19,51; 22,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,04; 20,78</t>
+          <t>17,92; 20,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,48; 20,83</t>
+          <t>19,68; 21,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,95; 13,53</t>
+          <t>11,95; 13,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,6; 17,43</t>
+          <t>15,63; 17,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,23; 15,97</t>
+          <t>14,07; 15,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,91; 17,4</t>
+          <t>16,45; 18,23</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95153</t>
+          <t>104156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>138156</t>
+          <t>148844</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>233309</t>
+          <t>252999</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43248; 71649</t>
+          <t>43684; 70389</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73477; 110183</t>
+          <t>71695; 109695</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70780; 107138</t>
+          <t>71153; 106961</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79289; 114124</t>
+          <t>85110; 123353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71155; 105536</t>
+          <t>68914; 103609</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>128489; 174328</t>
+          <t>131890; 175762</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>137242; 183390</t>
+          <t>134955; 181435</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>123448; 155201</t>
+          <t>134512; 168652</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>124085; 167001</t>
+          <t>123136; 166387</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>217049; 273249</t>
+          <t>215649; 272367</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>220108; 277933</t>
+          <t>218265; 277744</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>210660; 260361</t>
+          <t>227954; 281899</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115357</t>
+          <t>125433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>193821</t>
+          <t>218800</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>309178</t>
+          <t>344233</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77493; 114858</t>
+          <t>77316; 114415</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>108130; 152123</t>
+          <t>105544; 150650</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84792; 121348</t>
+          <t>83132; 126298</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51935; 154950</t>
+          <t>105148; 148330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>135981; 183848</t>
+          <t>132467; 181076</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>205873; 262494</t>
+          <t>205313; 261394</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>159562; 213948</t>
+          <t>160196; 211994</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>176106; 216834</t>
+          <t>197824; 240476</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>220557; 282358</t>
+          <t>223251; 282201</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>328414; 399549</t>
+          <t>325669; 394941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>256244; 324916</t>
+          <t>256582; 322897</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>206070; 361848</t>
+          <t>311548; 374792</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106989</t>
+          <t>116146</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>137827</t>
+          <t>160417</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>244817</t>
+          <t>276563</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45379; 74914</t>
+          <t>44514; 74218</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57915; 94288</t>
+          <t>58067; 93987</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49534; 80607</t>
+          <t>49302; 81352</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90256; 127607</t>
+          <t>96340; 138223</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>101186; 142351</t>
+          <t>102575; 142169</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>122002; 167024</t>
+          <t>122920; 166710</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>124032; 168839</t>
+          <t>125768; 169622</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66030; 185456</t>
+          <t>142965; 181449</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154112; 204754</t>
+          <t>154171; 203789</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>191419; 248391</t>
+          <t>190687; 245591</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181282; 241413</t>
+          <t>180512; 237385</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>167528; 292270</t>
+          <t>249641; 306376</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131221</t>
+          <t>135268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>228229</t>
+          <t>245972</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>359450</t>
+          <t>381240</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71366; 105987</t>
+          <t>71026; 103973</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>98334; 141370</t>
+          <t>98644; 141698</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83649; 123242</t>
+          <t>84952; 122880</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>110896; 152129</t>
+          <t>116372; 158391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>163783; 214830</t>
+          <t>163276; 213469</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>189022; 240934</t>
+          <t>187057; 239916</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>173488; 228333</t>
+          <t>171906; 224995</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>187818; 259044</t>
+          <t>223240; 270648</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>246602; 308948</t>
+          <t>248847; 311622</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>300559; 365555</t>
+          <t>297607; 365554</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>266461; 335079</t>
+          <t>267968; 337012</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>315034; 392635</t>
+          <t>349378; 412453</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>448719</t>
+          <t>481003</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>698033</t>
+          <t>774032</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1146752</t>
+          <t>1255035</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>264894; 336158</t>
+          <t>266224; 332220</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>373017; 456133</t>
+          <t>372736; 457774</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>323257; 393536</t>
+          <t>319716; 394196</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>344105; 500524</t>
+          <t>438177; 522614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>510656; 594358</t>
+          <t>509670; 596973</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>690758; 793204</t>
+          <t>694203; 793882</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>639480; 736634</t>
+          <t>635291; 741820</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>566674; 762632</t>
+          <t>734684; 817138</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>795588; 900460</t>
+          <t>795572; 901563</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1089810; 1217156</t>
+          <t>1091529; 1218293</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>987151; 1107887</t>
+          <t>976514; 1106741</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>990136; 1238738</t>
+          <t>1194796; 1324056</t>
         </is>
       </c>
     </row>
